--- a/crates/xlstream-eval/tests/fixtures/math/trigonometry.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/math/trigonometry.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">val</t>
   </si>
@@ -46,10 +43,10 @@
     <t xml:space="preserve">atan</t>
   </si>
   <si>
-    <t xml:space="preserve">atan2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi</t>
+    <t xml:space="preserve">atan2_val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pi_fn</t>
   </si>
 </sst>
 </file>
@@ -322,7 +319,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -353,406 +350,373 @@
       <c r="I1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>3.5</v>
+        <f aca="false">SIN(A2)</f>
+        <v>0</v>
       </c>
       <c r="C2" s="0" t="n">
-        <f aca="false">SIN(B2)</f>
-        <v>-0.35078322768962</v>
+        <f aca="false">COS(A2)</f>
+        <v>1</v>
       </c>
       <c r="D2" s="0" t="n">
-        <f aca="false">COS(B2)</f>
-        <v>-0.936456687290796</v>
+        <f aca="false">TAN(A2)</f>
+        <v>0</v>
       </c>
       <c r="E2" s="0" t="n">
-        <f aca="false">TAN(B2)</f>
-        <v>0.374585640158595</v>
+        <f aca="false">ASIN(A2/2)</f>
+        <v>0</v>
       </c>
       <c r="F2" s="0" t="n">
-        <f aca="false">ASIN(B2/100)</f>
-        <v>0.0350071497753487</v>
+        <f aca="false">ACOS(A2/2)</f>
+        <v>1.5707963267949</v>
       </c>
       <c r="G2" s="0" t="n">
-        <f aca="false">ACOS(B2/100)</f>
-        <v>1.53578917701955</v>
+        <f aca="false">ATAN(A2)</f>
+        <v>0</v>
       </c>
       <c r="H2" s="0" t="n">
-        <f aca="false">ATAN(B2)</f>
-        <v>1.29249666778979</v>
+        <f aca="false">ATAN2(1,A2)</f>
+        <v>0</v>
       </c>
       <c r="I2" s="0" t="n">
-        <f aca="false">ATAN2(A2,B2)</f>
-        <v>0.336674819386727</v>
-      </c>
-      <c r="J2" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>7.2</v>
+        <f aca="false">SIN(A3)</f>
+        <v>0.841470984807897</v>
       </c>
       <c r="C3" s="0" t="n">
-        <f aca="false">SIN(B3)</f>
-        <v>0.793667863849153</v>
+        <f aca="false">COS(A3)</f>
+        <v>0.54030230586814</v>
       </c>
       <c r="D3" s="0" t="n">
-        <f aca="false">COS(B3)</f>
-        <v>0.608351314532255</v>
+        <f aca="false">TAN(A3)</f>
+        <v>1.5574077246549</v>
       </c>
       <c r="E3" s="0" t="n">
-        <f aca="false">TAN(B3)</f>
-        <v>1.30462094005564</v>
+        <f aca="false">ASIN(A3/2)</f>
+        <v>0.523598775598299</v>
       </c>
       <c r="F3" s="0" t="n">
-        <f aca="false">ASIN(B3/100)</f>
-        <v>0.0720623535682035</v>
+        <f aca="false">ACOS(A3/2)</f>
+        <v>1.0471975511966</v>
       </c>
       <c r="G3" s="0" t="n">
-        <f aca="false">ACOS(B3/100)</f>
-        <v>1.49873397322669</v>
+        <f aca="false">ATAN(A3)</f>
+        <v>0.785398163397448</v>
       </c>
       <c r="H3" s="0" t="n">
-        <f aca="false">ATAN(B3)</f>
-        <v>1.43279030313738</v>
+        <f aca="false">ATAN2(1,A3)</f>
+        <v>0.785398163397448</v>
       </c>
       <c r="I3" s="0" t="n">
-        <f aca="false">ATAN2(A3,B3)</f>
-        <v>0.280411588283361</v>
-      </c>
-      <c r="J3" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <f aca="false">SIN(A4)</f>
+        <v>-0.841470984807897</v>
       </c>
       <c r="C4" s="0" t="n">
-        <f aca="false">SIN(B4)</f>
-        <v>0</v>
+        <f aca="false">COS(A4)</f>
+        <v>0.54030230586814</v>
       </c>
       <c r="D4" s="0" t="n">
-        <f aca="false">COS(B4)</f>
-        <v>1</v>
+        <f aca="false">TAN(A4)</f>
+        <v>-1.5574077246549</v>
       </c>
       <c r="E4" s="0" t="n">
-        <f aca="false">TAN(B4)</f>
-        <v>0</v>
+        <f aca="false">ASIN(A4/2)</f>
+        <v>-0.523598775598299</v>
       </c>
       <c r="F4" s="0" t="n">
-        <f aca="false">ASIN(B4/100)</f>
-        <v>0</v>
+        <f aca="false">ACOS(A4/2)</f>
+        <v>2.0943951023932</v>
       </c>
       <c r="G4" s="0" t="n">
-        <f aca="false">ACOS(B4/100)</f>
-        <v>1.5707963267949</v>
+        <f aca="false">ATAN(A4)</f>
+        <v>-0.785398163397448</v>
       </c>
       <c r="H4" s="0" t="n">
-        <f aca="false">ATAN(B4)</f>
-        <v>0</v>
+        <f aca="false">ATAN2(1,A4)</f>
+        <v>-0.785398163397448</v>
       </c>
       <c r="I4" s="0" t="n">
-        <f aca="false">ATAN2(A4,B4)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>15.8</v>
+        <f aca="false">SIN(A5)</f>
+        <v>0.479425538604203</v>
       </c>
       <c r="C5" s="0" t="n">
-        <f aca="false">SIN(B5)</f>
-        <v>-0.0919068502276817</v>
+        <f aca="false">COS(A5)</f>
+        <v>0.877582561890373</v>
       </c>
       <c r="D5" s="0" t="n">
-        <f aca="false">COS(B5)</f>
-        <v>-0.995767608873289</v>
+        <f aca="false">TAN(A5)</f>
+        <v>0.546302489843791</v>
       </c>
       <c r="E5" s="0" t="n">
-        <f aca="false">TAN(B5)</f>
-        <v>0.092297489302423</v>
+        <f aca="false">ASIN(A5/2)</f>
+        <v>0.252680255142079</v>
       </c>
       <c r="F5" s="0" t="n">
-        <f aca="false">ASIN(B5/100)</f>
-        <v>0.158664881904621</v>
+        <f aca="false">ACOS(A5/2)</f>
+        <v>1.31811607165282</v>
       </c>
       <c r="G5" s="0" t="n">
-        <f aca="false">ACOS(B5/100)</f>
-        <v>1.41213144489028</v>
+        <f aca="false">ATAN(A5)</f>
+        <v>0.463647609000806</v>
       </c>
       <c r="H5" s="0" t="n">
-        <f aca="false">ATAN(B5)</f>
-        <v>1.50758949489744</v>
+        <f aca="false">ATAN2(1,A5)</f>
+        <v>0.463647609000806</v>
       </c>
       <c r="I5" s="0" t="n">
-        <f aca="false">ATAN2(A5,B5)</f>
-        <v>0.156704578018935</v>
-      </c>
-      <c r="J5" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
+        <v>-0.5</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>-2.3</v>
+        <f aca="false">SIN(A6)</f>
+        <v>-0.479425538604203</v>
       </c>
       <c r="C6" s="0" t="n">
-        <f aca="false">SIN(B6)</f>
-        <v>-0.74570521217672</v>
+        <f aca="false">COS(A6)</f>
+        <v>0.877582561890373</v>
       </c>
       <c r="D6" s="0" t="n">
-        <f aca="false">COS(B6)</f>
-        <v>-0.666276021279824</v>
+        <f aca="false">TAN(A6)</f>
+        <v>-0.546302489843791</v>
       </c>
       <c r="E6" s="0" t="n">
-        <f aca="false">TAN(B6)</f>
-        <v>1.11921364173413</v>
+        <f aca="false">ASIN(A6/2)</f>
+        <v>-0.252680255142079</v>
       </c>
       <c r="F6" s="0" t="n">
-        <f aca="false">ASIN(B6/100)</f>
-        <v>-0.0230020283162111</v>
+        <f aca="false">ACOS(A6/2)</f>
+        <v>1.82347658193698</v>
       </c>
       <c r="G6" s="0" t="n">
-        <f aca="false">ACOS(B6/100)</f>
-        <v>1.59379835511111</v>
+        <f aca="false">ATAN(A6)</f>
+        <v>-0.463647609000806</v>
       </c>
       <c r="H6" s="0" t="n">
-        <f aca="false">ATAN(B6)</f>
-        <v>-1.16066898625341</v>
+        <f aca="false">ATAN2(1,A6)</f>
+        <v>-0.463647609000806</v>
       </c>
       <c r="I6" s="0" t="n">
-        <f aca="false">ATAN2(A6,B6)</f>
-        <v>-2.71045391287101</v>
-      </c>
-      <c r="J6" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>3.14159</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>8.1</v>
+        <f aca="false">SIN(A7)</f>
+        <v>2.65358979335273E-006</v>
       </c>
       <c r="C7" s="0" t="n">
-        <f aca="false">SIN(B7)</f>
-        <v>0.969889810845086</v>
+        <f aca="false">COS(A7)</f>
+        <v>-0.999999999996479</v>
       </c>
       <c r="D7" s="0" t="n">
-        <f aca="false">COS(B7)</f>
-        <v>-0.243544153735791</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <f aca="false">TAN(B7)</f>
-        <v>-3.98239824675599</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <f aca="false">ASIN(B7/100)</f>
-        <v>0.0810888360346978</v>
+        <f aca="false">TAN(A7)</f>
+        <v>-2.65358979336207E-006</v>
+      </c>
+      <c r="E7" s="0" t="e">
+        <f aca="false">ASIN(A7/2)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F7" s="0" t="e">
+        <f aca="false">ACOS(A7/2)</f>
+        <v>#NUM!</v>
       </c>
       <c r="G7" s="0" t="n">
-        <f aca="false">ACOS(B7/100)</f>
-        <v>1.4897074907602</v>
+        <f aca="false">ATAN(A7)</f>
+        <v>1.26262701154934</v>
       </c>
       <c r="H7" s="0" t="n">
-        <f aca="false">ATAN(B7)</f>
-        <v>1.447961087917</v>
+        <f aca="false">ATAN2(1,A7)</f>
+        <v>1.26262701154934</v>
       </c>
       <c r="I7" s="0" t="n">
-        <f aca="false">ATAN2(A7,B7)</f>
-        <v>0.160604729461027</v>
-      </c>
-      <c r="J7" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>75</v>
+        <v>0.1</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>4.6</v>
+        <f aca="false">SIN(A8)</f>
+        <v>0.0998334166468282</v>
       </c>
       <c r="C8" s="0" t="n">
-        <f aca="false">SIN(B8)</f>
-        <v>-0.993691003633464</v>
+        <f aca="false">COS(A8)</f>
+        <v>0.995004165278026</v>
       </c>
       <c r="D8" s="0" t="n">
-        <f aca="false">COS(B8)</f>
-        <v>-0.112152526935055</v>
+        <f aca="false">TAN(A8)</f>
+        <v>0.100334672085451</v>
       </c>
       <c r="E8" s="0" t="n">
-        <f aca="false">TAN(B8)</f>
-        <v>8.86017489564805</v>
+        <f aca="false">ASIN(A8/2)</f>
+        <v>0.05002085680577</v>
       </c>
       <c r="F8" s="0" t="n">
-        <f aca="false">ASIN(B8/100)</f>
-        <v>0.0460162381333741</v>
+        <f aca="false">ACOS(A8/2)</f>
+        <v>1.52077546998913</v>
       </c>
       <c r="G8" s="0" t="n">
-        <f aca="false">ACOS(B8/100)</f>
-        <v>1.52478008866152</v>
+        <f aca="false">ATAN(A8)</f>
+        <v>0.099668652491162</v>
       </c>
       <c r="H8" s="0" t="n">
-        <f aca="false">ATAN(B8)</f>
-        <v>1.35673564323108</v>
+        <f aca="false">ATAN2(1,A8)</f>
+        <v>0.099668652491162</v>
       </c>
       <c r="I8" s="0" t="n">
-        <f aca="false">ATAN2(A8,B8)</f>
-        <v>0.06125659899674</v>
-      </c>
-      <c r="J8" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.5</v>
+        <f aca="false">SIN(A9)</f>
+        <v>0.909297426825682</v>
       </c>
       <c r="C9" s="0" t="n">
-        <f aca="false">SIN(B9)</f>
-        <v>0.479425538604203</v>
+        <f aca="false">COS(A9)</f>
+        <v>-0.416146836547142</v>
       </c>
       <c r="D9" s="0" t="n">
-        <f aca="false">COS(B9)</f>
-        <v>0.877582561890373</v>
+        <f aca="false">TAN(A9)</f>
+        <v>-2.18503986326152</v>
       </c>
       <c r="E9" s="0" t="n">
-        <f aca="false">TAN(B9)</f>
-        <v>0.546302489843791</v>
+        <f aca="false">ASIN(A9/2)</f>
+        <v>1.5707963267949</v>
       </c>
       <c r="F9" s="0" t="n">
-        <f aca="false">ASIN(B9/100)</f>
-        <v>0.00500002083356771</v>
+        <f aca="false">ACOS(A9/2)</f>
+        <v>0</v>
       </c>
       <c r="G9" s="0" t="n">
-        <f aca="false">ACOS(B9/100)</f>
-        <v>1.56579630596133</v>
+        <f aca="false">ATAN(A9)</f>
+        <v>1.10714871779409</v>
       </c>
       <c r="H9" s="0" t="n">
-        <f aca="false">ATAN(B9)</f>
-        <v>0.463647609000806</v>
+        <f aca="false">ATAN2(1,A9)</f>
+        <v>1.10714871779409</v>
       </c>
       <c r="I9" s="0" t="n">
-        <f aca="false">ATAN2(A9,B9)</f>
-        <v>0.463647609000806</v>
-      </c>
-      <c r="J9" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>999</v>
+        <v>-2</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>12.4</v>
+        <f aca="false">SIN(A10)</f>
+        <v>-0.909297426825682</v>
       </c>
       <c r="C10" s="0" t="n">
-        <f aca="false">SIN(B10)</f>
-        <v>-0.165604175448309</v>
+        <f aca="false">COS(A10)</f>
+        <v>-0.416146836547142</v>
       </c>
       <c r="D10" s="0" t="n">
-        <f aca="false">COS(B10)</f>
-        <v>0.986192302278864</v>
+        <f aca="false">TAN(A10)</f>
+        <v>2.18503986326152</v>
       </c>
       <c r="E10" s="0" t="n">
-        <f aca="false">TAN(B10)</f>
-        <v>-0.167922802749156</v>
+        <f aca="false">ASIN(A10/2)</f>
+        <v>-1.5707963267949</v>
       </c>
       <c r="F10" s="0" t="n">
-        <f aca="false">ASIN(B10/100)</f>
-        <v>0.124319989721965</v>
+        <f aca="false">ACOS(A10/2)</f>
+        <v>3.14159265358979</v>
       </c>
       <c r="G10" s="0" t="n">
-        <f aca="false">ACOS(B10/100)</f>
-        <v>1.44647633707293</v>
+        <f aca="false">ATAN(A10)</f>
+        <v>-1.10714871779409</v>
       </c>
       <c r="H10" s="0" t="n">
-        <f aca="false">ATAN(B10)</f>
-        <v>1.49032531552944</v>
+        <f aca="false">ATAN2(1,A10)</f>
+        <v>-1.10714871779409</v>
       </c>
       <c r="I10" s="0" t="n">
-        <f aca="false">ATAN2(A10,B10)</f>
-        <v>0.0124117750195555</v>
-      </c>
-      <c r="J10" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>42</v>
+        <v>0.75</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>6.7</v>
+        <f aca="false">SIN(A11)</f>
+        <v>0.681638760023334</v>
       </c>
       <c r="C11" s="0" t="n">
-        <f aca="false">SIN(B11)</f>
-        <v>0.404849920616598</v>
+        <f aca="false">COS(A11)</f>
+        <v>0.731688868873821</v>
       </c>
       <c r="D11" s="0" t="n">
-        <f aca="false">COS(B11)</f>
-        <v>0.914383148235319</v>
+        <f aca="false">TAN(A11)</f>
+        <v>0.931596459944072</v>
       </c>
       <c r="E11" s="0" t="n">
-        <f aca="false">TAN(B11)</f>
-        <v>0.442757416732716</v>
+        <f aca="false">ASIN(A11/2)</f>
+        <v>0.384396774495639</v>
       </c>
       <c r="F11" s="0" t="n">
-        <f aca="false">ASIN(B11/100)</f>
-        <v>0.0670502286974465</v>
+        <f aca="false">ACOS(A11/2)</f>
+        <v>1.18639955229926</v>
       </c>
       <c r="G11" s="0" t="n">
-        <f aca="false">ACOS(B11/100)</f>
-        <v>1.50374609809745</v>
+        <f aca="false">ATAN(A11)</f>
+        <v>0.643501108793284</v>
       </c>
       <c r="H11" s="0" t="n">
-        <f aca="false">ATAN(B11)</f>
-        <v>1.42263630606307</v>
+        <f aca="false">ATAN2(1,A11)</f>
+        <v>0.643501108793284</v>
       </c>
       <c r="I11" s="0" t="n">
-        <f aca="false">ATAN2(A11,B11)</f>
-        <v>0.158190923438198</v>
-      </c>
-      <c r="J11" s="0" t="n">
         <f aca="false">PI()</f>
         <v>3.14159265358979</v>
       </c>
